--- a/气劲/通用气劲.xlsx
+++ b/气劲/通用气劲.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2356" uniqueCount="1727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2362" uniqueCount="1732">
   <si>
     <t>__meta = {</t>
   </si>
@@ -5143,6 +5143,21 @@
   </si>
   <si>
     <t>输出伤害波动-伤腰大附魔增伤5%</t>
+  </si>
+  <si>
+    <t>眩晕·致盲</t>
+  </si>
+  <si>
+    <t>据点·家园创意食品·盛·致盲</t>
+  </si>
+  <si>
+    <t>晕</t>
+  </si>
+  <si>
+    <t>#FFFF00FF</t>
+  </si>
+  <si>
+    <t>#FFFF00</t>
   </si>
   <si>
     <t>枯木</t>
@@ -6443,7 +6458,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1785582480000,</v>
+        <v>nTimeStamp = 1790936134000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -19465,7 +19480,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AS15"/>
+  <dimension ref="A1:AS16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:45">
@@ -19631,7 +19646,7 @@
         <v>613</v>
       </c>
       <c r="AQ3" t="str">
-        <f t="shared" ref="AQ3:AQ15" si="0">IF(B3&lt;&gt;"",IF(IFERROR(VALUE(C2),0)&lt;=0,"["&amp;B3&amp;"]={","},["&amp;B3&amp;"]={"),IF(C3&gt;0,"{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"nIcon="&amp;F3&amp;",","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&gt;0,"bCheckLevel=true,","")&amp;IF(I3&gt;0,"nScrutinyType="&amp;I3&amp;",","")&amp;IF(J3&lt;&gt;"","tKungFu={"&amp;J3&amp;"},","")&amp;IF(K3&lt;&gt;"","szNote="""&amp;K3&amp;""",","")&amp;IF(L3&lt;&gt;"","col={"&amp;L3&amp;"},","")&amp;"[1]={"&amp;IF(M3&lt;&gt;"","tMark={"&amp;M3&amp;"},","")&amp;IF(N3&lt;&gt;"","szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P3&gt;0,"bTeamChannel=true,","")&amp;IF(Q3&gt;0,"bWhisperChannel=true,","")&amp;IF(R3&gt;0,"bCenterAlarm=true,","")&amp;IF(S3&gt;0,"bScreenHead=true,","")&amp;IF(T3&gt;0,"bPartyBuffList=true,","")&amp;IF(U3&gt;0,"bBuffList=true,","")&amp;IF(V3&gt;0,"bFullScreen=true,","")&amp;IF(W3&gt;0,"bTeamPanel=true,","")&amp;IF(X3&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y3&lt;&gt;"","szVoice="""&amp;Y3&amp;""",","")&amp;IF(Z3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA3&gt;0,"bTeamChannel=true,","")&amp;IF(AB3&gt;0,"bWhisperChannel=true,","")&amp;IF(AC3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD3&gt;0,AH3&lt;&gt;"",AI3&gt;0,AJ3&lt;&gt;"",AK3&lt;&gt;"",AL3&gt;0,AM3&gt;0,AN3&gt;0,AO3&gt;0),"aCataclysmBuff={{"&amp;IF(AD3&gt;0,"nStackNum="&amp;AD3&amp;",","")&amp;IF(AE3&lt;&gt;"","szStackOp="""&amp;AE3&amp;""",","")&amp;IF(AF3&gt;0,"bOnlyMine=true,","")&amp;IF(AG3&gt;0,"bOnlyMe=true,","")&amp;IF(AH3&lt;&gt;"","szReminder="""&amp;AH3&amp;""",","")&amp;IF(AI3&gt;0,"nPriority="&amp;AI3&amp;",","")&amp;IF(AJ3&lt;&gt;"","col="""&amp;AJ3&amp;""",","")&amp;IF(AK3&lt;&gt;"","colScreenHead="""&amp;AK3&amp;""",","")&amp;IF(AL3&gt;0,"nColAlpha="&amp;AL3&amp;",","")&amp;IF(AM3&gt;0,"bAttention=true,","")&amp;IF(AN3&gt;0,"bCaution=true,","")&amp;IF(AO3&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP3&amp;"},","")&amp;IF(AR3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR3:AAC3)&amp;"},","")&amp;"},",IF(C2&gt;0,"},","")&amp;IF(AND(B3="",C3="",OR(B2&lt;&gt;"",C2&lt;&gt;"")),"},}","")))</f>
+        <f t="shared" ref="AQ3:AQ16" si="0">IF(B3&lt;&gt;"",IF(IFERROR(VALUE(C2),0)&lt;=0,"["&amp;B3&amp;"]={","},["&amp;B3&amp;"]={"),IF(C3&gt;0,"{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"nIcon="&amp;F3&amp;",","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&gt;0,"bCheckLevel=true,","")&amp;IF(I3&gt;0,"nScrutinyType="&amp;I3&amp;",","")&amp;IF(J3&lt;&gt;"","tKungFu={"&amp;J3&amp;"},","")&amp;IF(K3&lt;&gt;"","szNote="""&amp;K3&amp;""",","")&amp;IF(L3&lt;&gt;"","col={"&amp;L3&amp;"},","")&amp;"[1]={"&amp;IF(M3&lt;&gt;"","tMark={"&amp;M3&amp;"},","")&amp;IF(N3&lt;&gt;"","szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P3&gt;0,"bTeamChannel=true,","")&amp;IF(Q3&gt;0,"bWhisperChannel=true,","")&amp;IF(R3&gt;0,"bCenterAlarm=true,","")&amp;IF(S3&gt;0,"bScreenHead=true,","")&amp;IF(T3&gt;0,"bPartyBuffList=true,","")&amp;IF(U3&gt;0,"bBuffList=true,","")&amp;IF(V3&gt;0,"bFullScreen=true,","")&amp;IF(W3&gt;0,"bTeamPanel=true,","")&amp;IF(X3&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y3&lt;&gt;"","szVoice="""&amp;Y3&amp;""",","")&amp;IF(Z3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA3&gt;0,"bTeamChannel=true,","")&amp;IF(AB3&gt;0,"bWhisperChannel=true,","")&amp;IF(AC3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD3&gt;0,AH3&lt;&gt;"",AI3&gt;0,AJ3&lt;&gt;"",AK3&lt;&gt;"",AL3&gt;0,AM3&gt;0,AN3&gt;0,AO3&gt;0),"aCataclysmBuff={{"&amp;IF(AD3&gt;0,"nStackNum="&amp;AD3&amp;",","")&amp;IF(AE3&lt;&gt;"","szStackOp="""&amp;AE3&amp;""",","")&amp;IF(AF3&gt;0,"bOnlyMine=true,","")&amp;IF(AG3&gt;0,"bOnlyMe=true,","")&amp;IF(AH3&lt;&gt;"","szReminder="""&amp;AH3&amp;""",","")&amp;IF(AI3&gt;0,"nPriority="&amp;AI3&amp;",","")&amp;IF(AJ3&lt;&gt;"","col="""&amp;AJ3&amp;""",","")&amp;IF(AK3&lt;&gt;"","colScreenHead="""&amp;AK3&amp;""",","")&amp;IF(AL3&gt;0,"nColAlpha="&amp;AL3&amp;",","")&amp;IF(AM3&gt;0,"bAttention=true,","")&amp;IF(AN3&gt;0,"bCaution=true,","")&amp;IF(AO3&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP3&amp;"},","")&amp;IF(AR3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR3:AAC3)&amp;"},","")&amp;"},",IF(C2&gt;0,"},","")&amp;IF(AND(B3="",C3="",OR(B2&lt;&gt;"",C2&lt;&gt;"")),"},}","")))</f>
         <v>{dwID=27689,nLevel=1,nScrutinyType=1,szNote="缘会·今夕何夕",col={0,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=21596,nFrame=5,nTime=0,szName="缘会·今夕何夕",key="缘会·今夕何夕",},{nClass=2,nIcon=21596,nFrame=2,nTime=60,szName="香膏·绝世奇遇·已消失",key="缘会·今夕何夕",},},},</v>
       </c>
       <c r="AR3" s="1" t="s">
@@ -19790,26 +19805,23 @@
     </row>
     <row r="9" spans="1:45">
       <c r="C9">
-        <v>21953</v>
+        <v>812</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="J9" t="s">
-        <v>1641</v>
+      <c r="G9" t="s">
+        <v>1700</v>
       </c>
       <c r="K9" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="L9" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="S9">
         <v>1</v>
       </c>
-      <c r="T9">
-        <v>1</v>
-      </c>
       <c r="U9">
         <v>1</v>
       </c>
@@ -19817,31 +19829,31 @@
         <v>1</v>
       </c>
       <c r="AH9" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="AI9">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AJ9" t="s">
-        <v>1702</v>
+        <v>1703</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>1704</v>
       </c>
       <c r="AL9">
         <v>255</v>
       </c>
+      <c r="AO9">
+        <v>1</v>
+      </c>
       <c r="AQ9" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=21953,nLevel=1,tKungFu={["SKILL#10028"]=true,["SKILL#10080"]=true,["SKILL#10176"]=true,["SKILL#10448"]=true,["SKILL#10626"]=true,},szNote="枯木",col={255,150,0,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="枯",nPriority=6,col="#FA9B00FF",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=15422,nFrame=6,nTime="1,奶【{$receiver}】;2,奶【{$receiver}】;3,奶【{$receiver}】;30,奶【{$receiver}】",szName="1,奶【{$receiver}】;2,奶【{$receiver}】;3,奶【{$receiver}】;30,奶【{$receiver}】;",key="枯木{$receiver}",},{nClass=2,nIcon=15422,nFrame=6,nTime=0,szName="",key="枯木{$receiver}",},},},</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>1703</v>
-      </c>
-      <c r="AS9" t="s">
-        <v>1704</v>
+        <v>{dwID=812,nLevel=1,szName="眩晕·致盲",szNote="据点·家园创意食品·盛·致盲",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="10" spans="1:45">
       <c r="C10">
-        <v>20554</v>
+        <v>21953</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -19850,7 +19862,7 @@
         <v>1641</v>
       </c>
       <c r="K10" t="s">
-        <v>1700</v>
+        <v>1705</v>
       </c>
       <c r="L10" t="s">
         <v>596</v>
@@ -19868,73 +19880,94 @@
         <v>1</v>
       </c>
       <c r="AH10" t="s">
-        <v>1701</v>
+        <v>1706</v>
       </c>
       <c r="AI10">
         <v>6</v>
       </c>
       <c r="AJ10" t="s">
-        <v>1705</v>
+        <v>1707</v>
       </c>
       <c r="AL10">
         <v>255</v>
       </c>
       <c r="AQ10" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=20554,nLevel=1,tKungFu={["SKILL#10028"]=true,["SKILL#10080"]=true,["SKILL#10176"]=true,["SKILL#10448"]=true,["SKILL#10626"]=true,},szNote="枯木",col={255,150,0,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="枯",nPriority=6,col="#FF9600FF",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=15422,nFrame=6,nTime="1,奶【{$receiver}】;2,奶【{$receiver}】;3,奶【{$receiver}】;30,奶【{$receiver}】",szName="1,奶[{$receiver}];2,奶[{$receiver}];3,奶[{$receiver}];30,奶[{$receiver}];",key="枯木{$receiver}",},{nClass=2,nIcon=15422,nFrame=5,nTime=0,szName="",key="枯木{$receiver}",},},},</v>
+        <v>{dwID=21953,nLevel=1,tKungFu={["SKILL#10028"]=true,["SKILL#10080"]=true,["SKILL#10176"]=true,["SKILL#10448"]=true,["SKILL#10626"]=true,},szNote="枯木",col={255,150,0,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="枯",nPriority=6,col="#FA9B00FF",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=15422,nFrame=6,nTime="1,奶【{$receiver}】;2,奶【{$receiver}】;3,奶【{$receiver}】;30,奶【{$receiver}】",szName="1,奶【{$receiver}】;2,奶【{$receiver}】;3,奶【{$receiver}】;30,奶【{$receiver}】;",key="枯木{$receiver}",},{nClass=2,nIcon=15422,nFrame=6,nTime=0,szName="",key="枯木{$receiver}",},},},</v>
       </c>
       <c r="AR10" t="s">
+        <v>1708</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="11" spans="1:45">
+      <c r="C11">
+        <v>20554</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="J11" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K11" t="s">
+        <v>1705</v>
+      </c>
+      <c r="L11" t="s">
+        <v>596</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="s">
         <v>1706</v>
       </c>
-      <c r="AS10" t="s">
-        <v>1707</v>
-      </c>
-    </row>
-    <row r="11" spans="1:45">
-      <c r="A11" t="s">
-        <v>1648</v>
-      </c>
-      <c r="B11">
-        <v>-3</v>
+      <c r="AI11">
+        <v>6</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>1710</v>
+      </c>
+      <c r="AL11">
+        <v>255</v>
       </c>
       <c r="AQ11" t="str">
         <f t="shared" si="0"/>
-        <v>},[-3]={</v>
+        <v>{dwID=20554,nLevel=1,tKungFu={["SKILL#10028"]=true,["SKILL#10080"]=true,["SKILL#10176"]=true,["SKILL#10448"]=true,["SKILL#10626"]=true,},szNote="枯木",col={255,150,0,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="枯",nPriority=6,col="#FF9600FF",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=15422,nFrame=6,nTime="1,奶【{$receiver}】;2,奶【{$receiver}】;3,奶【{$receiver}】;30,奶【{$receiver}】",szName="1,奶[{$receiver}];2,奶[{$receiver}];3,奶[{$receiver}];30,奶[{$receiver}];",key="枯木{$receiver}",},{nClass=2,nIcon=15422,nFrame=5,nTime=0,szName="",key="枯木{$receiver}",},},},</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>1711</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>1712</v>
       </c>
     </row>
     <row r="12" spans="1:45">
-      <c r="C12">
-        <v>2316</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="AF12">
-        <v>1</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>1708</v>
-      </c>
-      <c r="AI12">
-        <v>5</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>1667</v>
-      </c>
-      <c r="AL12">
-        <v>255</v>
-      </c>
-      <c r="AM12">
-        <v>1</v>
+      <c r="A12" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B12">
+        <v>-3</v>
       </c>
       <c r="AQ12" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=2316,nLevel=1,[1]={},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="蛊",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+        <v>},[-3]={</v>
       </c>
     </row>
     <row r="13" spans="1:45">
       <c r="C13">
-        <v>26986</v>
+        <v>2316</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -19943,7 +19976,7 @@
         <v>1</v>
       </c>
       <c r="AH13" t="s">
-        <v>1709</v>
+        <v>1713</v>
       </c>
       <c r="AI13">
         <v>5</v>
@@ -19959,47 +19992,77 @@
       </c>
       <c r="AQ13" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=26986,nLevel=1,[1]={},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="音",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+        <v>{dwID=2316,nLevel=1,[1]={},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="蛊",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
       </c>
     </row>
     <row r="14" spans="1:45">
       <c r="C14">
-        <v>9335</v>
+        <v>26986</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
-      <c r="F14">
-        <v>11863</v>
-      </c>
-      <c r="K14" t="s">
-        <v>1710</v>
-      </c>
-      <c r="L14" t="s">
-        <v>1711</v>
-      </c>
       <c r="AF14">
         <v>1</v>
       </c>
       <c r="AH14" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
       <c r="AI14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="s">
-        <v>1713</v>
+        <v>1667</v>
       </c>
       <c r="AL14">
         <v>255</v>
       </c>
+      <c r="AM14">
+        <v>1</v>
+      </c>
       <c r="AQ14" t="str">
         <f t="shared" si="0"/>
+        <v>{dwID=26986,nLevel=1,[1]={},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="音",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="15" spans="1:45">
+      <c r="C15">
+        <v>9335</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>11863</v>
+      </c>
+      <c r="K15" t="s">
+        <v>1715</v>
+      </c>
+      <c r="L15" t="s">
+        <v>1716</v>
+      </c>
+      <c r="AF15">
+        <v>1</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>1717</v>
+      </c>
+      <c r="AI15">
+        <v>3</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>1718</v>
+      </c>
+      <c r="AL15">
+        <v>255</v>
+      </c>
+      <c r="AQ15" t="str">
+        <f t="shared" si="0"/>
         <v>{dwID=9335,nLevel=1,nIcon=11863,szNote="无法获得梅花三弄",col={255,238,255,},[1]={},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="落",nPriority=3,col="#FFEEEEFF",nColAlpha=255,},},},</v>
       </c>
     </row>
-    <row r="15" spans="1:45">
-      <c r="AQ15" t="str">
+    <row r="16" spans="1:45">
+      <c r="AQ16" t="str">
         <f t="shared" si="0"/>
         <v>},},}</v>
       </c>
@@ -20052,43 +20115,43 @@
         <v>1484</v>
       </c>
       <c r="L1" t="s">
-        <v>1714</v>
+        <v>1719</v>
       </c>
       <c r="M1" t="s">
-        <v>1715</v>
+        <v>1720</v>
       </c>
       <c r="N1" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="O1" t="s">
-        <v>1717</v>
+        <v>1722</v>
       </c>
       <c r="P1" t="s">
-        <v>1718</v>
+        <v>1723</v>
       </c>
       <c r="Q1" t="s">
-        <v>1719</v>
+        <v>1724</v>
       </c>
       <c r="R1" t="s">
-        <v>1720</v>
+        <v>1725</v>
       </c>
       <c r="S1" t="s">
-        <v>1721</v>
+        <v>1726</v>
       </c>
       <c r="T1" t="s">
-        <v>1722</v>
+        <v>1727</v>
       </c>
       <c r="U1" t="s">
-        <v>1723</v>
+        <v>1728</v>
       </c>
       <c r="V1" t="s">
-        <v>1724</v>
+        <v>1729</v>
       </c>
       <c r="W1" t="s">
-        <v>1725</v>
+        <v>1730</v>
       </c>
       <c r="X1" t="s">
-        <v>1726</v>
+        <v>1731</v>
       </c>
       <c r="Y1" t="s">
         <v>316</v>

--- a/气劲/通用气劲.xlsx
+++ b/气劲/通用气劲.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2362" uniqueCount="1732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2365" uniqueCount="1734">
   <si>
     <t>__meta = {</t>
   </si>
@@ -5098,6 +5098,12 @@
   </si>
   <si>
     <t>return {DEBUFF={</t>
+  </si>
+  <si>
+    <t>切奇穴</t>
+  </si>
+  <si>
+    <t>武学助手CD</t>
   </si>
   <si>
     <t>缘会·今夕何夕</t>
@@ -6458,7 +6464,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1790936134000,</v>
+        <v>nTimeStamp = 1790958026000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -19480,7 +19486,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AS16"/>
+  <dimension ref="A1:AS17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:45">
@@ -19629,36 +19635,36 @@
         <v>[-1]={</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:45">
-      <c r="C3" s="1">
-        <v>27689</v>
-      </c>
-      <c r="D3" s="1">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1" t="s">
+    <row r="3" customFormat="1" spans="1:45">
+      <c r="C3">
+        <v>8613</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
         <v>1685</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>613</v>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>1686</v>
+      </c>
+      <c r="L3" t="s">
+        <v>604</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
       </c>
       <c r="AQ3" t="str">
-        <f t="shared" ref="AQ3:AQ16" si="0">IF(B3&lt;&gt;"",IF(IFERROR(VALUE(C2),0)&lt;=0,"["&amp;B3&amp;"]={","},["&amp;B3&amp;"]={"),IF(C3&gt;0,"{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"nIcon="&amp;F3&amp;",","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&gt;0,"bCheckLevel=true,","")&amp;IF(I3&gt;0,"nScrutinyType="&amp;I3&amp;",","")&amp;IF(J3&lt;&gt;"","tKungFu={"&amp;J3&amp;"},","")&amp;IF(K3&lt;&gt;"","szNote="""&amp;K3&amp;""",","")&amp;IF(L3&lt;&gt;"","col={"&amp;L3&amp;"},","")&amp;"[1]={"&amp;IF(M3&lt;&gt;"","tMark={"&amp;M3&amp;"},","")&amp;IF(N3&lt;&gt;"","szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P3&gt;0,"bTeamChannel=true,","")&amp;IF(Q3&gt;0,"bWhisperChannel=true,","")&amp;IF(R3&gt;0,"bCenterAlarm=true,","")&amp;IF(S3&gt;0,"bScreenHead=true,","")&amp;IF(T3&gt;0,"bPartyBuffList=true,","")&amp;IF(U3&gt;0,"bBuffList=true,","")&amp;IF(V3&gt;0,"bFullScreen=true,","")&amp;IF(W3&gt;0,"bTeamPanel=true,","")&amp;IF(X3&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y3&lt;&gt;"","szVoice="""&amp;Y3&amp;""",","")&amp;IF(Z3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA3&gt;0,"bTeamChannel=true,","")&amp;IF(AB3&gt;0,"bWhisperChannel=true,","")&amp;IF(AC3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD3&gt;0,AH3&lt;&gt;"",AI3&gt;0,AJ3&lt;&gt;"",AK3&lt;&gt;"",AL3&gt;0,AM3&gt;0,AN3&gt;0,AO3&gt;0),"aCataclysmBuff={{"&amp;IF(AD3&gt;0,"nStackNum="&amp;AD3&amp;",","")&amp;IF(AE3&lt;&gt;"","szStackOp="""&amp;AE3&amp;""",","")&amp;IF(AF3&gt;0,"bOnlyMine=true,","")&amp;IF(AG3&gt;0,"bOnlyMe=true,","")&amp;IF(AH3&lt;&gt;"","szReminder="""&amp;AH3&amp;""",","")&amp;IF(AI3&gt;0,"nPriority="&amp;AI3&amp;",","")&amp;IF(AJ3&lt;&gt;"","col="""&amp;AJ3&amp;""",","")&amp;IF(AK3&lt;&gt;"","colScreenHead="""&amp;AK3&amp;""",","")&amp;IF(AL3&gt;0,"nColAlpha="&amp;AL3&amp;",","")&amp;IF(AM3&gt;0,"bAttention=true,","")&amp;IF(AN3&gt;0,"bCaution=true,","")&amp;IF(AO3&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP3&amp;"},","")&amp;IF(AR3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR3:AAC3)&amp;"},","")&amp;"},",IF(C2&gt;0,"},","")&amp;IF(AND(B3="",C3="",OR(B2&lt;&gt;"",C2&lt;&gt;"")),"},}","")))</f>
-        <v>{dwID=27689,nLevel=1,nScrutinyType=1,szNote="缘会·今夕何夕",col={0,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=21596,nFrame=5,nTime=0,szName="缘会·今夕何夕",key="缘会·今夕何夕",},{nClass=2,nIcon=21596,nFrame=2,nTime=60,szName="香膏·绝世奇遇·已消失",key="缘会·今夕何夕",},},},</v>
-      </c>
-      <c r="AR3" s="1" t="s">
-        <v>1686</v>
-      </c>
-      <c r="AS3" s="1" t="s">
-        <v>1687</v>
+        <f t="shared" ref="AQ3:AQ17" si="0">IF(B3&lt;&gt;"",IF(IFERROR(VALUE(C2),0)&lt;=0,"["&amp;B3&amp;"]={","},["&amp;B3&amp;"]={"),IF(C3&gt;0,"{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"nIcon="&amp;F3&amp;",","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&gt;0,"bCheckLevel=true,","")&amp;IF(I3&gt;0,"nScrutinyType="&amp;I3&amp;",","")&amp;IF(J3&lt;&gt;"","tKungFu={"&amp;J3&amp;"},","")&amp;IF(K3&lt;&gt;"","szNote="""&amp;K3&amp;""",","")&amp;IF(L3&lt;&gt;"","col={"&amp;L3&amp;"},","")&amp;"[1]={"&amp;IF(M3&lt;&gt;"","tMark={"&amp;M3&amp;"},","")&amp;IF(N3&lt;&gt;"","szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P3&gt;0,"bTeamChannel=true,","")&amp;IF(Q3&gt;0,"bWhisperChannel=true,","")&amp;IF(R3&gt;0,"bCenterAlarm=true,","")&amp;IF(S3&gt;0,"bScreenHead=true,","")&amp;IF(T3&gt;0,"bPartyBuffList=true,","")&amp;IF(U3&gt;0,"bBuffList=true,","")&amp;IF(V3&gt;0,"bFullScreen=true,","")&amp;IF(W3&gt;0,"bTeamPanel=true,","")&amp;IF(X3&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y3&lt;&gt;"","szVoice="""&amp;Y3&amp;""",","")&amp;IF(Z3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA3&gt;0,"bTeamChannel=true,","")&amp;IF(AB3&gt;0,"bWhisperChannel=true,","")&amp;IF(AC3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD3&gt;0,AH3&lt;&gt;"",AI3&gt;0,AJ3&lt;&gt;"",AK3&lt;&gt;"",AL3&gt;0,AM3&gt;0,AN3&gt;0,AO3&gt;0),"aCataclysmBuff={{"&amp;IF(AD3&gt;0,"nStackNum="&amp;AD3&amp;",","")&amp;IF(AE3&lt;&gt;"","szStackOp="""&amp;AE3&amp;""",","")&amp;IF(AF3&gt;0,"bOnlyMine=true,","")&amp;IF(AG3&gt;0,"bOnlyMe=true,","")&amp;IF(AH3&lt;&gt;"","szReminder="""&amp;AH3&amp;""",","")&amp;IF(AI3&gt;0,"nPriority="&amp;AI3&amp;",","")&amp;IF(AJ3&lt;&gt;"","col="""&amp;AJ3&amp;""",","")&amp;IF(AK3&lt;&gt;"","colScreenHead="""&amp;AK3&amp;""",","")&amp;IF(AL3&gt;0,"nColAlpha="&amp;AL3&amp;",","")&amp;IF(AM3&gt;0,"bAttention=true,","")&amp;IF(AN3&gt;0,"bCaution=true,","")&amp;IF(AO3&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP3&amp;"},","")&amp;IF(AR3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR3:AAC3)&amp;"},","")&amp;"},",IF(C2&gt;0,"},","")&amp;IF(AND(B3="",C3="",OR(B2&lt;&gt;"",C2&lt;&gt;"")),"},}","")))</f>
+        <v>{dwID=8613,nLevel=1,szName="切奇穴",nScrutinyType=1,szNote="武学助手CD",col={255,255,0,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:45">
       <c r="C4" s="1">
-        <v>27663</v>
+        <v>27689</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
@@ -19667,25 +19673,25 @@
         <v>1</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>613</v>
       </c>
       <c r="AQ4" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=27663,nLevel=1,nScrutinyType=1,szNote="缘会·月出皎兮",col={0,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=21600,nFrame=5,nTime=0,szName="缘会·月出皎兮",key="缘会·月出皎兮",},{nClass=2,nIcon=21600,nFrame=2,nTime=60,szName="香膏·普通奇遇·已消失",key="缘会·月出皎兮",},},},</v>
+        <v>{dwID=27689,nLevel=1,nScrutinyType=1,szNote="缘会·今夕何夕",col={0,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=21596,nFrame=5,nTime=0,szName="缘会·今夕何夕",key="缘会·今夕何夕",},{nClass=2,nIcon=21596,nFrame=2,nTime=60,szName="香膏·绝世奇遇·已消失",key="缘会·今夕何夕",},},},</v>
       </c>
       <c r="AR4" s="1" t="s">
+        <v>1688</v>
+      </c>
+      <c r="AS4" s="1" t="s">
         <v>1689</v>
-      </c>
-      <c r="AS4" s="1" t="s">
-        <v>1690</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:45">
       <c r="C5" s="1">
-        <v>27662</v>
+        <v>27663</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -19694,65 +19700,59 @@
         <v>1</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>613</v>
       </c>
       <c r="AQ5" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=27662,nLevel=1,nScrutinyType=1,szNote="缘会·山有扶苏",col={0,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=21600,nFrame=5,nTime=0,szName="缘会·山有扶苏",key="缘会·山有扶苏",},{nClass=2,nIcon=21600,nFrame=2,nTime=60,szName="香膏·宠物奇遇·已消失",key="缘会·山有扶苏",},},},</v>
+        <v>{dwID=27663,nLevel=1,nScrutinyType=1,szNote="缘会·月出皎兮",col={0,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=21600,nFrame=5,nTime=0,szName="缘会·月出皎兮",key="缘会·月出皎兮",},{nClass=2,nIcon=21600,nFrame=2,nTime=60,szName="香膏·普通奇遇·已消失",key="缘会·月出皎兮",},},},</v>
       </c>
       <c r="AR5" s="1" t="s">
+        <v>1691</v>
+      </c>
+      <c r="AS5" s="1" t="s">
         <v>1692</v>
       </c>
-      <c r="AS5" s="1" t="s">
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:45">
+      <c r="C6" s="1">
+        <v>27662</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>1693</v>
       </c>
-    </row>
-    <row r="6" spans="1:45">
-      <c r="C6">
-        <v>30710</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1694</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>1695</v>
-      </c>
-      <c r="L6" t="s">
-        <v>622</v>
-      </c>
-      <c r="U6">
-        <v>1</v>
+      <c r="L6" s="1" t="s">
+        <v>613</v>
       </c>
       <c r="AQ6" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=30710,nLevel=1,szName="头计数",nScrutinyType=1,szNote="3次后额外伤害或治疗",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=27662,nLevel=1,nScrutinyType=1,szNote="缘会·山有扶苏",col={0,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=21600,nFrame=5,nTime=0,szName="缘会·山有扶苏",key="缘会·山有扶苏",},{nClass=2,nIcon=21600,nFrame=2,nTime=60,szName="香膏·宠物奇遇·已消失",key="缘会·山有扶苏",},},},</v>
+      </c>
+      <c r="AR6" s="1" t="s">
+        <v>1694</v>
+      </c>
+      <c r="AS6" s="1" t="s">
+        <v>1695</v>
       </c>
     </row>
     <row r="7" spans="1:45">
       <c r="C7">
-        <v>15455</v>
+        <v>30710</v>
       </c>
       <c r="D7">
         <v>1</v>
-      </c>
-      <c r="F7">
-        <v>7293</v>
       </c>
       <c r="G7" t="s">
         <v>1696</v>
       </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
       <c r="I7">
         <v>1</v>
       </c>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="AQ7" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=15455,nLevel=1,nIcon=7293,szName="1%腰",bCheckLevel=true,nScrutinyType=1,szNote="输出伤害波动-伤腰大附魔增伤1%",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=30710,nLevel=1,szName="头计数",nScrutinyType=1,szNote="3次后额外伤害或治疗",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="8" spans="1:45">
@@ -19775,10 +19775,10 @@
         <v>15455</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>7371</v>
+        <v>7293</v>
       </c>
       <c r="G8" t="s">
         <v>1698</v>
@@ -19800,111 +19800,93 @@
       </c>
       <c r="AQ8" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=15455,nLevel=2,nIcon=7371,szName="5%腰",bCheckLevel=true,nScrutinyType=1,szNote="输出伤害波动-伤腰大附魔增伤5%",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=15455,nLevel=1,nIcon=7293,szName="1%腰",bCheckLevel=true,nScrutinyType=1,szNote="输出伤害波动-伤腰大附魔增伤1%",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="9" spans="1:45">
       <c r="C9">
-        <v>812</v>
+        <v>15455</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>7371</v>
       </c>
       <c r="G9" t="s">
         <v>1700</v>
       </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
       <c r="K9" t="s">
         <v>1701</v>
       </c>
       <c r="L9" t="s">
-        <v>604</v>
-      </c>
-      <c r="S9">
-        <v>1</v>
+        <v>622</v>
       </c>
       <c r="U9">
-        <v>1</v>
-      </c>
-      <c r="W9">
-        <v>1</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>1702</v>
-      </c>
-      <c r="AI9">
-        <v>13</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>1703</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>1704</v>
-      </c>
-      <c r="AL9">
-        <v>255</v>
-      </c>
-      <c r="AO9">
         <v>1</v>
       </c>
       <c r="AQ9" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=812,nLevel=1,szName="眩晕·致盲",szNote="据点·家园创意食品·盛·致盲",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
+        <v>{dwID=15455,nLevel=2,nIcon=7371,szName="5%腰",bCheckLevel=true,nScrutinyType=1,szNote="输出伤害波动-伤腰大附魔增伤5%",col={0,255,255,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="10" spans="1:45">
       <c r="C10">
-        <v>21953</v>
+        <v>812</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="J10" t="s">
-        <v>1641</v>
+      <c r="G10" t="s">
+        <v>1702</v>
       </c>
       <c r="K10" t="s">
+        <v>1703</v>
+      </c>
+      <c r="L10" t="s">
+        <v>604</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AI10">
+        <v>13</v>
+      </c>
+      <c r="AJ10" t="s">
         <v>1705</v>
       </c>
-      <c r="L10" t="s">
-        <v>596</v>
-      </c>
-      <c r="S10">
-        <v>1</v>
-      </c>
-      <c r="T10">
-        <v>1</v>
-      </c>
-      <c r="U10">
-        <v>1</v>
-      </c>
-      <c r="W10">
-        <v>1</v>
-      </c>
-      <c r="AH10" t="s">
+      <c r="AK10" t="s">
         <v>1706</v>
-      </c>
-      <c r="AI10">
-        <v>6</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>1707</v>
       </c>
       <c r="AL10">
         <v>255</v>
       </c>
+      <c r="AO10">
+        <v>1</v>
+      </c>
       <c r="AQ10" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=21953,nLevel=1,tKungFu={["SKILL#10028"]=true,["SKILL#10080"]=true,["SKILL#10176"]=true,["SKILL#10448"]=true,["SKILL#10626"]=true,},szNote="枯木",col={255,150,0,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="枯",nPriority=6,col="#FA9B00FF",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=15422,nFrame=6,nTime="1,奶【{$receiver}】;2,奶【{$receiver}】;3,奶【{$receiver}】;30,奶【{$receiver}】",szName="1,奶【{$receiver}】;2,奶【{$receiver}】;3,奶【{$receiver}】;30,奶【{$receiver}】;",key="枯木{$receiver}",},{nClass=2,nIcon=15422,nFrame=6,nTime=0,szName="",key="枯木{$receiver}",},},},</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>1708</v>
-      </c>
-      <c r="AS10" t="s">
-        <v>1709</v>
+        <v>{dwID=812,nLevel=1,szName="眩晕·致盲",szNote="据点·家园创意食品·盛·致盲",col={255,255,0,},[1]={bScreenHead=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="晕",nPriority=13,col="#FFFF00FF",colScreenHead="#FFFF00",nColAlpha=255,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="11" spans="1:45">
       <c r="C11">
-        <v>20554</v>
+        <v>21953</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -19913,7 +19895,7 @@
         <v>1641</v>
       </c>
       <c r="K11" t="s">
-        <v>1705</v>
+        <v>1707</v>
       </c>
       <c r="L11" t="s">
         <v>596</v>
@@ -19931,73 +19913,94 @@
         <v>1</v>
       </c>
       <c r="AH11" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
       <c r="AI11">
         <v>6</v>
       </c>
       <c r="AJ11" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="AL11">
         <v>255</v>
       </c>
       <c r="AQ11" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=20554,nLevel=1,tKungFu={["SKILL#10028"]=true,["SKILL#10080"]=true,["SKILL#10176"]=true,["SKILL#10448"]=true,["SKILL#10626"]=true,},szNote="枯木",col={255,150,0,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="枯",nPriority=6,col="#FF9600FF",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=15422,nFrame=6,nTime="1,奶【{$receiver}】;2,奶【{$receiver}】;3,奶【{$receiver}】;30,奶【{$receiver}】",szName="1,奶[{$receiver}];2,奶[{$receiver}];3,奶[{$receiver}];30,奶[{$receiver}];",key="枯木{$receiver}",},{nClass=2,nIcon=15422,nFrame=5,nTime=0,szName="",key="枯木{$receiver}",},},},</v>
+        <v>{dwID=21953,nLevel=1,tKungFu={["SKILL#10028"]=true,["SKILL#10080"]=true,["SKILL#10176"]=true,["SKILL#10448"]=true,["SKILL#10626"]=true,},szNote="枯木",col={255,150,0,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="枯",nPriority=6,col="#FA9B00FF",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=15422,nFrame=6,nTime="1,奶【{$receiver}】;2,奶【{$receiver}】;3,奶【{$receiver}】;30,奶【{$receiver}】",szName="1,奶【{$receiver}】;2,奶【{$receiver}】;3,奶【{$receiver}】;30,奶【{$receiver}】;",key="枯木{$receiver}",},{nClass=2,nIcon=15422,nFrame=6,nTime=0,szName="",key="枯木{$receiver}",},},},</v>
       </c>
       <c r="AR11" t="s">
+        <v>1710</v>
+      </c>
+      <c r="AS11" t="s">
         <v>1711</v>
       </c>
-      <c r="AS11" t="s">
+    </row>
+    <row r="12" spans="1:45">
+      <c r="C12">
+        <v>20554</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K12" t="s">
+        <v>1707</v>
+      </c>
+      <c r="L12" t="s">
+        <v>596</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>1708</v>
+      </c>
+      <c r="AI12">
+        <v>6</v>
+      </c>
+      <c r="AJ12" t="s">
         <v>1712</v>
       </c>
-    </row>
-    <row r="12" spans="1:45">
-      <c r="A12" t="s">
-        <v>1648</v>
-      </c>
-      <c r="B12">
-        <v>-3</v>
+      <c r="AL12">
+        <v>255</v>
       </c>
       <c r="AQ12" t="str">
         <f t="shared" si="0"/>
-        <v>},[-3]={</v>
+        <v>{dwID=20554,nLevel=1,tKungFu={["SKILL#10028"]=true,["SKILL#10080"]=true,["SKILL#10176"]=true,["SKILL#10448"]=true,["SKILL#10626"]=true,},szNote="枯木",col={255,150,0,},[1]={bScreenHead=true,bPartyBuffList=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="枯",nPriority=6,col="#FF9600FF",nColAlpha=255,},},tCountdown={{nClass=1,nIcon=15422,nFrame=6,nTime="1,奶【{$receiver}】;2,奶【{$receiver}】;3,奶【{$receiver}】;30,奶【{$receiver}】",szName="1,奶[{$receiver}];2,奶[{$receiver}];3,奶[{$receiver}];30,奶[{$receiver}];",key="枯木{$receiver}",},{nClass=2,nIcon=15422,nFrame=5,nTime=0,szName="",key="枯木{$receiver}",},},},</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>1713</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>1714</v>
       </c>
     </row>
     <row r="13" spans="1:45">
-      <c r="C13">
-        <v>2316</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="AF13">
-        <v>1</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>1713</v>
-      </c>
-      <c r="AI13">
-        <v>5</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>1667</v>
-      </c>
-      <c r="AL13">
-        <v>255</v>
-      </c>
-      <c r="AM13">
-        <v>1</v>
+      <c r="A13" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B13">
+        <v>-3</v>
       </c>
       <c r="AQ13" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=2316,nLevel=1,[1]={},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="蛊",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+        <v>},[-3]={</v>
       </c>
     </row>
     <row r="14" spans="1:45">
       <c r="C14">
-        <v>26986</v>
+        <v>2316</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -20006,7 +20009,7 @@
         <v>1</v>
       </c>
       <c r="AH14" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="AI14">
         <v>5</v>
@@ -20022,47 +20025,77 @@
       </c>
       <c r="AQ14" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=26986,nLevel=1,[1]={},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="音",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+        <v>{dwID=2316,nLevel=1,[1]={},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="蛊",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
       </c>
     </row>
     <row r="15" spans="1:45">
       <c r="C15">
-        <v>9335</v>
+        <v>26986</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
-      <c r="F15">
-        <v>11863</v>
-      </c>
-      <c r="K15" t="s">
-        <v>1715</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="AF15">
+        <v>1</v>
+      </c>
+      <c r="AH15" t="s">
         <v>1716</v>
       </c>
-      <c r="AF15">
-        <v>1</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>1717</v>
-      </c>
       <c r="AI15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ15" t="s">
-        <v>1718</v>
+        <v>1667</v>
       </c>
       <c r="AL15">
         <v>255</v>
       </c>
+      <c r="AM15">
+        <v>1</v>
+      </c>
       <c r="AQ15" t="str">
         <f t="shared" si="0"/>
+        <v>{dwID=26986,nLevel=1,[1]={},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="音",nPriority=5,col="#00EE00FF",nColAlpha=255,bAttention=true,},},},</v>
+      </c>
+    </row>
+    <row r="16" spans="1:45">
+      <c r="C16">
+        <v>9335</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>11863</v>
+      </c>
+      <c r="K16" t="s">
+        <v>1717</v>
+      </c>
+      <c r="L16" t="s">
+        <v>1718</v>
+      </c>
+      <c r="AF16">
+        <v>1</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>1719</v>
+      </c>
+      <c r="AI16">
+        <v>3</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>1720</v>
+      </c>
+      <c r="AL16">
+        <v>255</v>
+      </c>
+      <c r="AQ16" t="str">
+        <f t="shared" si="0"/>
         <v>{dwID=9335,nLevel=1,nIcon=11863,szNote="无法获得梅花三弄",col={255,238,255,},[1]={},[2]={},aCataclysmBuff={{bOnlyMine=true,szReminder="落",nPriority=3,col="#FFEEEEFF",nColAlpha=255,},},},</v>
       </c>
     </row>
-    <row r="16" spans="1:45">
-      <c r="AQ16" t="str">
+    <row r="17" spans="43:43">
+      <c r="AQ17" t="str">
         <f t="shared" si="0"/>
         <v>},},}</v>
       </c>
@@ -20115,43 +20148,43 @@
         <v>1484</v>
       </c>
       <c r="L1" t="s">
-        <v>1719</v>
+        <v>1721</v>
       </c>
       <c r="M1" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="N1" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="O1" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="P1" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
       <c r="Q1" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="R1" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="S1" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="T1" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="U1" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
       <c r="V1" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="W1" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="X1" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="Y1" t="s">
         <v>316</v>

--- a/气劲/通用气劲.xlsx
+++ b/气劲/通用气劲.xlsx
@@ -6464,7 +6464,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1790958026000,</v>
+        <v>nTimeStamp = 1791105015000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -19642,6 +19642,9 @@
       <c r="D3">
         <v>1</v>
       </c>
+      <c r="F3">
+        <v>630</v>
+      </c>
       <c r="G3" t="s">
         <v>1685</v>
       </c>
@@ -19659,7 +19662,7 @@
       </c>
       <c r="AQ3" t="str">
         <f t="shared" ref="AQ3:AQ17" si="0">IF(B3&lt;&gt;"",IF(IFERROR(VALUE(C2),0)&lt;=0,"["&amp;B3&amp;"]={","},["&amp;B3&amp;"]={"),IF(C3&gt;0,"{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"nIcon="&amp;F3&amp;",","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&gt;0,"bCheckLevel=true,","")&amp;IF(I3&gt;0,"nScrutinyType="&amp;I3&amp;",","")&amp;IF(J3&lt;&gt;"","tKungFu={"&amp;J3&amp;"},","")&amp;IF(K3&lt;&gt;"","szNote="""&amp;K3&amp;""",","")&amp;IF(L3&lt;&gt;"","col={"&amp;L3&amp;"},","")&amp;"[1]={"&amp;IF(M3&lt;&gt;"","tMark={"&amp;M3&amp;"},","")&amp;IF(N3&lt;&gt;"","szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P3&gt;0,"bTeamChannel=true,","")&amp;IF(Q3&gt;0,"bWhisperChannel=true,","")&amp;IF(R3&gt;0,"bCenterAlarm=true,","")&amp;IF(S3&gt;0,"bScreenHead=true,","")&amp;IF(T3&gt;0,"bPartyBuffList=true,","")&amp;IF(U3&gt;0,"bBuffList=true,","")&amp;IF(V3&gt;0,"bFullScreen=true,","")&amp;IF(W3&gt;0,"bTeamPanel=true,","")&amp;IF(X3&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y3&lt;&gt;"","szVoice="""&amp;Y3&amp;""",","")&amp;IF(Z3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA3&gt;0,"bTeamChannel=true,","")&amp;IF(AB3&gt;0,"bWhisperChannel=true,","")&amp;IF(AC3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD3&gt;0,AH3&lt;&gt;"",AI3&gt;0,AJ3&lt;&gt;"",AK3&lt;&gt;"",AL3&gt;0,AM3&gt;0,AN3&gt;0,AO3&gt;0),"aCataclysmBuff={{"&amp;IF(AD3&gt;0,"nStackNum="&amp;AD3&amp;",","")&amp;IF(AE3&lt;&gt;"","szStackOp="""&amp;AE3&amp;""",","")&amp;IF(AF3&gt;0,"bOnlyMine=true,","")&amp;IF(AG3&gt;0,"bOnlyMe=true,","")&amp;IF(AH3&lt;&gt;"","szReminder="""&amp;AH3&amp;""",","")&amp;IF(AI3&gt;0,"nPriority="&amp;AI3&amp;",","")&amp;IF(AJ3&lt;&gt;"","col="""&amp;AJ3&amp;""",","")&amp;IF(AK3&lt;&gt;"","colScreenHead="""&amp;AK3&amp;""",","")&amp;IF(AL3&gt;0,"nColAlpha="&amp;AL3&amp;",","")&amp;IF(AM3&gt;0,"bAttention=true,","")&amp;IF(AN3&gt;0,"bCaution=true,","")&amp;IF(AO3&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP3&amp;"},","")&amp;IF(AR3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR3:AAC3)&amp;"},","")&amp;"},",IF(C2&gt;0,"},","")&amp;IF(AND(B3="",C3="",OR(B2&lt;&gt;"",C2&lt;&gt;"")),"},}","")))</f>
-        <v>{dwID=8613,nLevel=1,szName="切奇穴",nScrutinyType=1,szNote="武学助手CD",col={255,255,0,},[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=8613,nLevel=1,nIcon=630,szName="切奇穴",nScrutinyType=1,szNote="武学助手CD",col={255,255,0,},[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:45">
